--- a/data/trans_orig/LAWTONB_2R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R3-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28563</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17740</t>
+          <t>16736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58769</t>
+          <t>60099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86426</t>
+          <t>86847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101621</t>
+          <t>102036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110766</t>
+          <t>113621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131795</t>
+          <t>132799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205755</t>
+          <t>204425</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229914</t>
+          <t>229231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27250</t>
+          <t>27198</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51433</t>
+          <t>50794</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44250</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72372</t>
+          <t>72315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115378</t>
+          <t>116440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133186</t>
+          <t>133428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131247</t>
+          <t>131886</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155430</t>
+          <t>155482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>256196</t>
+          <t>256253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>284318</t>
+          <t>284116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27495</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21694</t>
+          <t>21739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85125</t>
+          <t>85456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98574</t>
+          <t>98532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108355</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124255</t>
+          <t>124294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>197050</t>
+          <t>196713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218527</t>
+          <t>218482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>20467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33348</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56334</t>
+          <t>56043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>44624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72583</t>
+          <t>71824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116720</t>
+          <t>116750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128978</t>
+          <t>128924</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152443</t>
+          <t>152734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175429</t>
+          <t>177180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273412</t>
+          <t>274171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301678</t>
+          <t>301371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51284</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164711</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216682</t>
+          <t>215710</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422082</t>
+          <t>421166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>451182</t>
+          <t>449662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>529131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>571200</t>
+          <t>571019</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>962626</t>
+          <t>963598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1014597</t>
+          <t>1014316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34579</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33845</t>
+          <t>32958</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56929</t>
+          <t>56103</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56249</t>
+          <t>55264</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>85935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104968</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123353</t>
+          <t>122999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109858</t>
+          <t>110684</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>132942</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220936</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250085</t>
+          <t>251070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,96%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>48080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74644</t>
+          <t>74078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80272</t>
+          <t>80719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116876</t>
+          <t>114518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105354</t>
+          <t>105335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127816</t>
+          <t>127697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116776</t>
+          <t>117342</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144020</t>
+          <t>143340</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229422</t>
+          <t>231780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>266026</t>
+          <t>265579</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>13958</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32630</t>
+          <t>32752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>30684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>53430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>50823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80469</t>
+          <t>79102</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70968</t>
+          <t>70846</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89901</t>
+          <t>89640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86532</t>
+          <t>87589</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109963</t>
+          <t>110335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164148</t>
+          <t>165515</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193610</t>
+          <t>193794</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43989</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35405</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>62122</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>64866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>97806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117624</t>
+          <t>116196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140109</t>
+          <t>139440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182944</t>
+          <t>181628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208345</t>
+          <t>207380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>308333</t>
+          <t>307557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341062</t>
+          <t>340497</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137651</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172810</t>
+          <t>171588</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223623</t>
+          <t>219962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278494</t>
+          <t>281438</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>421986</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>462199</t>
+          <t>464284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519352</t>
+          <t>523013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>570165</t>
+          <t>571387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959542</t>
+          <t>960424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1024118</t>
+          <t>1021174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32855</t>
+          <t>33345</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54115</t>
+          <t>53253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51848</t>
+          <t>52162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80592</t>
+          <t>82163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>103389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120100</t>
+          <t>120710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119276</t>
+          <t>120138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143110</t>
+          <t>142763</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>229533</t>
+          <t>227962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>258277</t>
+          <t>257963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>37084</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>41003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71605</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65877</t>
+          <t>65037</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100224</t>
+          <t>98280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128718</t>
+          <t>127857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146548</t>
+          <t>145406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147558</t>
+          <t>148629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176983</t>
+          <t>178160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>283880</t>
+          <t>285824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318227</t>
+          <t>319067</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29704</t>
+          <t>28687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53634</t>
+          <t>51757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42484</t>
+          <t>42307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70178</t>
+          <t>69885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,13%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>92570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>106825</t>
+          <t>107053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88962</t>
+          <t>90839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112892</t>
+          <t>113909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187453</t>
+          <t>187746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215147</t>
+          <t>215324</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>15704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33149</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33981</t>
+          <t>33739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62779</t>
+          <t>61139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>54839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86411</t>
+          <t>89294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141469</t>
+          <t>141172</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159576</t>
+          <t>158914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180002</t>
+          <t>181642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>208800</t>
+          <t>209042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330989</t>
+          <t>328106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>362098</t>
+          <t>362561</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>160121</t>
+          <t>157849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>212250</t>
+          <t>210046</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242771</t>
+          <t>241978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>306347</t>
+          <t>303179</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>485254</t>
+          <t>485103</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>519036</t>
+          <t>517253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>565681</t>
+          <t>567885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>620082</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1062912</t>
+          <t>1066080</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1126488</t>
+          <t>1127281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37371</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>32071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46498</t>
+          <t>49448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>62521</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>58105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>76198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>106437</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89053</t>
+          <t>94420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112182</t>
+          <t>120242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>110712</t>
+          <t>123337</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101585</t>
+          <t>113866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119224</t>
+          <t>131243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>115612</t>
+          <t>123343</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>108516</t>
+          <t>113605</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>124372</t>
+          <t>131698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>226323</t>
+          <t>246680</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214034</t>
+          <t>232875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237163</t>
+          <t>258697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>73,26%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>31636</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>40519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>70963</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55236</t>
+          <t>60597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74081</t>
+          <t>81927</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>89802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107702</t>
+          <t>117708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>130875</t>
+          <t>146568</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122409</t>
+          <t>137685</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137554</t>
+          <t>154118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>153239</t>
+          <t>169764</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143444</t>
+          <t>158800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>180130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>284115</t>
+          <t>316331</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269938</t>
+          <t>301222</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>294564</t>
+          <t>329128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12392</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7752</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19344</t>
+          <t>21022</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>34828</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98454</t>
+          <t>52335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>56959</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>45974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95304</t>
+          <t>68333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>123067</t>
+          <t>144549</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>116115</t>
+          <t>137135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127707</t>
+          <t>149732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>320159</t>
+          <t>131091</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261349</t>
+          <t>122106</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348916</t>
+          <t>139613</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>443228</t>
+          <t>275639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>399959</t>
+          <t>264265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>475215</t>
+          <t>286624</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27630</t>
+          <t>28317</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>21233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>36616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67625</t>
+          <t>74609</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57440</t>
+          <t>63117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>86416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>95255</t>
+          <t>102925</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82657</t>
+          <t>88972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>109354</t>
+          <t>117573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>173118</t>
+          <t>182215</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164341</t>
+          <t>173916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180408</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>206137</t>
+          <t>218638</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194762</t>
+          <t>206831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216322</t>
+          <t>230130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>379255</t>
+          <t>400854</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365156</t>
+          <t>386206</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391853</t>
+          <t>414807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>97888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>130066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>123513</t>
+          <t>236056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>300052</t>
+          <t>274210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229064</t>
+          <t>344204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399571</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>537773</t>
+          <t>596668</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>520783</t>
+          <t>580141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551801</t>
+          <t>612319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>795147</t>
+          <t>642836</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>729172</t>
+          <t>624008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>905711</t>
+          <t>662162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1332920</t>
+          <t>1239504</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1274057</t>
+          <t>1212361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1444564</t>
+          <t>1264220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
